--- a/Plantilla_Maestro_Filtros_Demotron.xlsx
+++ b/Plantilla_Maestro_Filtros_Demotron.xlsx
@@ -8,26 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/18769b89b4824173/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{5FBDE2D1-A6BE-44AC-8C04-41CD297440BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF5D58A8-DB0A-49D5-912C-9522D1B82D0A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6852A39C-70CB-44A2-907A-3FFDF086D230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-1620" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Maestro de Filtros" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -36,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="55">
   <si>
     <t>Código Equipo</t>
   </si>
@@ -78,6 +67,9 @@
   </si>
   <si>
     <t>P558615</t>
+  </si>
+  <si>
+    <t>C00116152</t>
   </si>
   <si>
     <t>AIRE CABINA</t>
@@ -644,223 +636,243 @@
       <c r="G2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="2"/>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" s="3">
         <v>1</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="2">
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" s="3">
         <v>1</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" s="2">
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" s="2"/>
+        <v>32</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C7" s="3">
         <v>1</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H7" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C8" s="2">
         <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C9" s="3">
         <v>1</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H9" s="3"/>
+        <v>45</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C10" s="2">
         <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H10" s="2"/>
+        <v>50</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C11" s="3">
         <v>1</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="H11" s="3"/>
+        <v>54</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Plantilla_Maestro_Filtros_Demotron.xlsx
+++ b/Plantilla_Maestro_Filtros_Demotron.xlsx
@@ -1,31 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30128"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/18769b89b4824173/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6852A39C-70CB-44A2-907A-3FFDF086D230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="346" documentId="8_{5FBDE2D1-A6BE-44AC-8C04-41CD297440BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA0C4486-B5FF-4213-A9E8-402BA0A7A417}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1620" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Maestro de Filtros" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028" iterateDelta="1E-4"/>
   <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="186">
   <si>
     <t>Código Equipo</t>
   </si>
@@ -69,9 +80,6 @@
     <t>P558615</t>
   </si>
   <si>
-    <t>C00116152</t>
-  </si>
-  <si>
     <t>AIRE CABINA</t>
   </si>
   <si>
@@ -81,9 +89,6 @@
     <t>K1002210</t>
   </si>
   <si>
-    <t>(en blanco)</t>
-  </si>
-  <si>
     <t>AIRE PRIMARIO</t>
   </si>
   <si>
@@ -190,13 +195,412 @@
   </si>
   <si>
     <t>R010044</t>
+  </si>
+  <si>
+    <t>MD-79</t>
+  </si>
+  <si>
+    <t>RE504836</t>
+  </si>
+  <si>
+    <t>AT191102</t>
+  </si>
+  <si>
+    <t>AT178516</t>
+  </si>
+  <si>
+    <t>AT178517</t>
+  </si>
+  <si>
+    <t>DECANTADOR COMBUSTIBLE</t>
+  </si>
+  <si>
+    <t>RE541922</t>
+  </si>
+  <si>
+    <t>FILTRO DE COMBUSTIBLE</t>
+  </si>
+  <si>
+    <t>RE522878</t>
+  </si>
+  <si>
+    <t>RECIRCULACION CABINA</t>
+  </si>
+  <si>
+    <t>AT307501</t>
+  </si>
+  <si>
+    <t>RETEN ACEITE MOTOR</t>
+  </si>
+  <si>
+    <t>R502513</t>
+  </si>
+  <si>
+    <t>FILTRO RESPIRADERO ESTANQUE</t>
+  </si>
+  <si>
+    <t>T225008</t>
+  </si>
+  <si>
+    <t>MD-85</t>
+  </si>
+  <si>
+    <t>FILTRO ACEITE MOTOR</t>
+  </si>
+  <si>
+    <t>LF3642</t>
+  </si>
+  <si>
+    <t>ZUAC-00178</t>
+  </si>
+  <si>
+    <t>P550422</t>
+  </si>
+  <si>
+    <t>FILTRO COMBUSTIBLE ELEMENTO</t>
+  </si>
+  <si>
+    <t>ZUAC-00986</t>
+  </si>
+  <si>
+    <t>P502655</t>
+  </si>
+  <si>
+    <t>SN 30017</t>
+  </si>
+  <si>
+    <t>FILTRO COMBUSTIBLE</t>
+  </si>
+  <si>
+    <t>FS19551</t>
+  </si>
+  <si>
+    <t>11NA-72011VM</t>
+  </si>
+  <si>
+    <t>P551855</t>
+  </si>
+  <si>
+    <t>SN 909010</t>
+  </si>
+  <si>
+    <t>FILTRO LINEA FRENO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31LM-10310-AS </t>
+  </si>
+  <si>
+    <t>P584251</t>
+  </si>
+  <si>
+    <t>SH 75206</t>
+  </si>
+  <si>
+    <t>FILTRO ELEMENTO RESPIRADERO</t>
+  </si>
+  <si>
+    <t>AF26675</t>
+  </si>
+  <si>
+    <t>31EE-02110-A</t>
+  </si>
+  <si>
+    <t>P502563</t>
+  </si>
+  <si>
+    <t>SA 12572</t>
+  </si>
+  <si>
+    <t>FILTRO ACEITE TRANSMISION</t>
+  </si>
+  <si>
+    <t>HF6316</t>
+  </si>
+  <si>
+    <t>ZGAQ-03301-AS</t>
+  </si>
+  <si>
+    <t>P551757</t>
+  </si>
+  <si>
+    <t>SH 56366</t>
+  </si>
+  <si>
+    <t>FILTRO AIRE ACONDICIONADO</t>
+  </si>
+  <si>
+    <t>11U2-90170VMA</t>
+  </si>
+  <si>
+    <t>SC 80131</t>
+  </si>
+  <si>
+    <t>FILTRO AIRE ACONDICIONADO (2)</t>
+  </si>
+  <si>
+    <t>11U2-90180-AS</t>
+  </si>
+  <si>
+    <t>SC 80143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTRO HIDRAILICO RETORNO </t>
+  </si>
+  <si>
+    <t>31U2-60191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SH 60837 </t>
+  </si>
+  <si>
+    <t>FILTRO AIRE PRIMARIO</t>
+  </si>
+  <si>
+    <t>AF25557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11FQ-20250-AS </t>
+  </si>
+  <si>
+    <t>P772580</t>
+  </si>
+  <si>
+    <t>SA 16580</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTRO AIRE SECUNDARIO </t>
+  </si>
+  <si>
+    <t>AF25558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11FQ-20150 </t>
+  </si>
+  <si>
+    <t>P829333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SA 16302 </t>
+  </si>
+  <si>
+    <t>MD-107</t>
+  </si>
+  <si>
+    <t>LF4054</t>
+  </si>
+  <si>
+    <t>P502908</t>
+  </si>
+  <si>
+    <t>SO 15007</t>
+  </si>
+  <si>
+    <t>PREFILTRO DE COMBUSTIBLE</t>
+  </si>
+  <si>
+    <t>FS19769</t>
+  </si>
+  <si>
+    <t>P550778</t>
+  </si>
+  <si>
+    <t>CONJUNTO FILTRO MOTOR</t>
+  </si>
+  <si>
+    <t>160102100014B033</t>
+  </si>
+  <si>
+    <t>FF5770</t>
+  </si>
+  <si>
+    <t>160604020048B</t>
+  </si>
+  <si>
+    <t>R010018</t>
+  </si>
+  <si>
+    <t>SK 3320</t>
+  </si>
+  <si>
+    <t>FILTRO SEPARADOR DE COMBUSTIBLE</t>
+  </si>
+  <si>
+    <t>FS36235S</t>
+  </si>
+  <si>
+    <t>GLQ007201604</t>
+  </si>
+  <si>
+    <t>R010053</t>
+  </si>
+  <si>
+    <t>CD-118</t>
+  </si>
+  <si>
+    <t>FF5380</t>
+  </si>
+  <si>
+    <t>A0000901551</t>
+  </si>
+  <si>
+    <t>P550632</t>
+  </si>
+  <si>
+    <t>A0001801709</t>
+  </si>
+  <si>
+    <t>MD-49</t>
+  </si>
+  <si>
+    <t>FILTRO DE ACEITE</t>
+  </si>
+  <si>
+    <t>LF16520</t>
+  </si>
+  <si>
+    <t>FILTRO DE AIRE</t>
+  </si>
+  <si>
+    <t>FS19680</t>
+  </si>
+  <si>
+    <t>FS19821</t>
+  </si>
+  <si>
+    <t>FILTRO HIDRAULICO</t>
+  </si>
+  <si>
+    <t>HF35305</t>
+  </si>
+  <si>
+    <t>BT8439-MPG</t>
+  </si>
+  <si>
+    <t>P550486</t>
+  </si>
+  <si>
+    <t>HF35150</t>
+  </si>
+  <si>
+    <t>254686A2</t>
+  </si>
+  <si>
+    <t>CD-88</t>
+  </si>
+  <si>
+    <t>FILTRO ACEITE PAÑETE</t>
+  </si>
+  <si>
+    <t>51018046002SAMPA</t>
+  </si>
+  <si>
+    <t>FILTRO ELEMENTO DE ACEITE</t>
+  </si>
+  <si>
+    <t>LF16244</t>
+  </si>
+  <si>
+    <t>51.05504-0107</t>
+  </si>
+  <si>
+    <t>UFI 25.046.00</t>
+  </si>
+  <si>
+    <t>FILTRO COMBUSTIBLE C/ ANILLO</t>
+  </si>
+  <si>
+    <t>FF5629</t>
+  </si>
+  <si>
+    <t>UFI 26.011.00</t>
+  </si>
+  <si>
+    <t>FILTRO SEPARADOR COMBUSTIBLE</t>
+  </si>
+  <si>
+    <t>FS20147</t>
+  </si>
+  <si>
+    <t>81.12501-6096</t>
+  </si>
+  <si>
+    <t>UFI 24.035.01</t>
+  </si>
+  <si>
+    <t>FILTRO ELEMENTO AIRE (Prim)</t>
+  </si>
+  <si>
+    <t>AF25894</t>
+  </si>
+  <si>
+    <t>81.08405-0016</t>
+  </si>
+  <si>
+    <t>UFI 27.619.00</t>
+  </si>
+  <si>
+    <t>FILTRO ELEMENTO AIRE (Secu)</t>
+  </si>
+  <si>
+    <t>AF25896</t>
+  </si>
+  <si>
+    <t>81.08405-0017</t>
+  </si>
+  <si>
+    <t>UFI 27.616.00</t>
+  </si>
+  <si>
+    <t>FILTRO SECADOR DE AIRE</t>
+  </si>
+  <si>
+    <t>AD27747</t>
+  </si>
+  <si>
+    <t>81.52155-0045</t>
+  </si>
+  <si>
+    <t>K068350</t>
+  </si>
+  <si>
+    <t>FILTRO POLEN</t>
+  </si>
+  <si>
+    <t>AF26671</t>
+  </si>
+  <si>
+    <t>81.61910-0018</t>
+  </si>
+  <si>
+    <t>FILTRO DE UREA</t>
+  </si>
+  <si>
+    <t>FILTRO INTARDER TRANSMISIÓN</t>
+  </si>
+  <si>
+    <t>CD-87</t>
+  </si>
+  <si>
+    <t>CD-89</t>
+  </si>
+  <si>
+    <t>CD-90</t>
+  </si>
+  <si>
+    <t>CD-91</t>
+  </si>
+  <si>
+    <t>CD-94</t>
+  </si>
+  <si>
+    <t>CD-102</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -262,7 +666,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -270,7 +674,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -575,11 +982,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H176"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="2" max="2" width="37.85546875" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
@@ -588,7 +995,7 @@
     <col min="8" max="8" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -614,7 +1021,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -636,243 +1043,2961 @@
       <c r="G2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="3">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="2">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="C5" s="2">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="3">
-        <v>1</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="2">
-        <v>1</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="F6" s="2"/>
+      <c r="G6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="C7" s="2">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="3">
-        <v>1</v>
-      </c>
-      <c r="D7" s="3" t="s">
+      <c r="F7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="G7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="2">
-        <v>1</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="F8" s="2"/>
+      <c r="G8" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" s="2" t="s">
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="E9" s="2"/>
+      <c r="F9" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="3">
-        <v>1</v>
-      </c>
-      <c r="D9" s="3" t="s">
+      <c r="G9" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="2">
-        <v>1</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="C11" s="2">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="E11" s="2"/>
+      <c r="F11" s="2" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="3">
-        <v>1</v>
-      </c>
-      <c r="D11" s="3" t="s">
+      <c r="G11" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" s="3" t="s">
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="B12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="C13" s="2">
+        <v>1</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="2">
+        <v>1</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1</v>
+      </c>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="2">
+        <v>1</v>
+      </c>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="2">
+        <v>1</v>
+      </c>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1</v>
+      </c>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20" s="2">
+        <v>1</v>
+      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C21" s="2">
+        <v>1</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H21" s="2"/>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" s="2">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" s="2">
+        <v>1</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24" s="2">
+        <v>1</v>
+      </c>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" s="2">
+        <v>1</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" s="2">
+        <v>1</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C27" s="2">
+        <v>1</v>
+      </c>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C28" s="2">
+        <v>1</v>
+      </c>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C29" s="2">
+        <v>1</v>
+      </c>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C30" s="2">
+        <v>1</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C31" s="2">
+        <v>1</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32" s="2">
+        <v>1</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2">
+        <v>60328867</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C33" s="2">
+        <v>1</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2">
+        <v>60328868</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H33" s="2"/>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C34" s="2">
+        <v>1</v>
+      </c>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C35" s="2">
+        <v>1</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C36" s="2">
+        <v>1</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H36" s="2"/>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C37" s="2">
+        <v>1</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="H37" s="2"/>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C38" s="2">
+        <v>1</v>
+      </c>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C41" s="2">
+        <v>1</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C42" s="2">
+        <v>1</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C43" s="2">
+        <v>1</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C44" s="2">
+        <v>1</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C45" s="2">
+        <v>1</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="H45" s="2"/>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C46" s="2">
+        <v>1</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C47" s="2">
+        <v>1</v>
+      </c>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2">
+        <v>51018040044</v>
+      </c>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C48" s="2">
+        <v>1</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C49" s="2">
+        <v>1</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2">
+        <v>51125030061</v>
+      </c>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C50" s="2">
+        <v>1</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C51" s="2">
+        <v>1</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C52" s="2">
+        <v>1</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C53" s="2">
+        <v>1</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C54" s="2">
+        <v>1</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C55" s="2">
+        <v>1</v>
+      </c>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="4">
+        <v>81154030000</v>
+      </c>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C56" s="2">
+        <v>1</v>
+      </c>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="4">
+        <v>81321186010</v>
+      </c>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C57" s="2">
+        <v>1</v>
+      </c>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2">
+        <v>51018040044</v>
+      </c>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C58" s="2">
+        <v>1</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C59" s="2">
+        <v>1</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2">
+        <v>51125030061</v>
+      </c>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C60" s="2">
+        <v>1</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C61" s="2">
+        <v>1</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C62" s="2">
+        <v>1</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C63" s="2">
+        <v>1</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C64" s="2">
+        <v>1</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C65" s="2">
+        <v>1</v>
+      </c>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2">
+        <v>81154030000</v>
+      </c>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C66" s="2">
+        <v>1</v>
+      </c>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2">
+        <v>81321186010</v>
+      </c>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C67" s="2">
+        <v>1</v>
+      </c>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2">
+        <v>51018040044</v>
+      </c>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C68" s="2">
+        <v>1</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C69" s="2">
+        <v>1</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2">
+        <v>51125030061</v>
+      </c>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C70" s="2">
+        <v>1</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C71" s="2">
+        <v>1</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C72" s="2">
+        <v>1</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C73" s="2">
+        <v>1</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C74" s="2">
+        <v>1</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C75" s="2">
+        <v>1</v>
+      </c>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2">
+        <v>81154030000</v>
+      </c>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C76" s="2">
+        <v>1</v>
+      </c>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2">
+        <v>81321186010</v>
+      </c>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C77" s="2">
+        <v>1</v>
+      </c>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2">
+        <v>51018040044</v>
+      </c>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C78" s="2">
+        <v>1</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C79" s="2">
+        <v>1</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2">
+        <v>51125030061</v>
+      </c>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C80" s="2">
+        <v>1</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="G80" s="2"/>
+      <c r="H80" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C81" s="2">
+        <v>1</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C82" s="2">
+        <v>1</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="G82" s="2"/>
+      <c r="H82" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C83" s="2">
+        <v>1</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C84" s="2">
+        <v>1</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="G84" s="2"/>
+      <c r="H84" s="2"/>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C85" s="2">
+        <v>1</v>
+      </c>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="2">
+        <v>81154030000</v>
+      </c>
+      <c r="G85" s="2"/>
+      <c r="H85" s="2"/>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C86" s="2">
+        <v>1</v>
+      </c>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+      <c r="F86" s="2">
+        <v>81321186010</v>
+      </c>
+      <c r="G86" s="2"/>
+      <c r="H86" s="2"/>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C87" s="2">
+        <v>1</v>
+      </c>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
+      <c r="F87" s="2">
+        <v>51018040044</v>
+      </c>
+      <c r="G87" s="2"/>
+      <c r="H87" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C88" s="2">
+        <v>1</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G88" s="2"/>
+      <c r="H88" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C89" s="2">
+        <v>1</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" s="2">
+        <v>51125030061</v>
+      </c>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C90" s="2">
+        <v>1</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="G90" s="2"/>
+      <c r="H90" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C91" s="2">
+        <v>1</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C92" s="2">
+        <v>1</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="G92" s="2"/>
+      <c r="H92" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C93" s="2">
+        <v>1</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="G93" s="2"/>
+      <c r="H93" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C94" s="2">
+        <v>1</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="G94" s="2"/>
+      <c r="H94" s="2"/>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C95" s="2">
+        <v>1</v>
+      </c>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
+      <c r="F95" s="2">
+        <v>81154030000</v>
+      </c>
+      <c r="G95" s="2"/>
+      <c r="H95" s="2"/>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C96" s="2">
+        <v>1</v>
+      </c>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2"/>
+      <c r="F96" s="2">
+        <v>81321186010</v>
+      </c>
+      <c r="G96" s="2"/>
+      <c r="H96" s="2"/>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C97" s="2">
+        <v>1</v>
+      </c>
+      <c r="D97" s="2"/>
+      <c r="E97" s="2"/>
+      <c r="F97" s="2">
+        <v>51018040044</v>
+      </c>
+      <c r="G97" s="2"/>
+      <c r="H97" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C98" s="2">
+        <v>1</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C99" s="2">
+        <v>1</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" s="2">
+        <v>51125030061</v>
+      </c>
+      <c r="G99" s="2"/>
+      <c r="H99" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C100" s="2">
+        <v>1</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="G100" s="2"/>
+      <c r="H100" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C101" s="2">
+        <v>1</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G101" s="2"/>
+      <c r="H101" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C102" s="2">
+        <v>1</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="G102" s="2"/>
+      <c r="H102" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C103" s="2">
+        <v>1</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="G103" s="2"/>
+      <c r="H103" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C104" s="2">
+        <v>1</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="G104" s="2"/>
+      <c r="H104" s="2"/>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C105" s="2">
+        <v>1</v>
+      </c>
+      <c r="D105" s="2"/>
+      <c r="E105" s="2"/>
+      <c r="F105" s="2">
+        <v>81154030000</v>
+      </c>
+      <c r="G105" s="2"/>
+      <c r="H105" s="2"/>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C106" s="2">
+        <v>1</v>
+      </c>
+      <c r="D106" s="2"/>
+      <c r="E106" s="2"/>
+      <c r="F106" s="2">
+        <v>81321186010</v>
+      </c>
+      <c r="G106" s="2"/>
+      <c r="H106" s="2"/>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C107" s="2">
+        <v>1</v>
+      </c>
+      <c r="D107" s="2"/>
+      <c r="E107" s="2"/>
+      <c r="F107" s="2">
+        <v>51018040044</v>
+      </c>
+      <c r="G107" s="2"/>
+      <c r="H107" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C108" s="2">
+        <v>1</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G108" s="2"/>
+      <c r="H108" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
+      <c r="A109" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C109" s="2">
+        <v>1</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" s="2">
+        <v>51125030061</v>
+      </c>
+      <c r="G109" s="2"/>
+      <c r="H109" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
+      <c r="A110" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C110" s="2">
+        <v>1</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="G110" s="2"/>
+      <c r="H110" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
+      <c r="A111" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C111" s="2">
+        <v>1</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E111" s="2"/>
+      <c r="F111" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G111" s="2"/>
+      <c r="H111" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
+      <c r="A112" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C112" s="2">
+        <v>1</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="G112" s="2"/>
+      <c r="H112" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C113" s="2">
+        <v>1</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E113" s="2"/>
+      <c r="F113" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="G113" s="2"/>
+      <c r="H113" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="A114" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C114" s="2">
+        <v>1</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E114" s="2"/>
+      <c r="F114" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="G114" s="2"/>
+      <c r="H114" s="2"/>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="A115" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C115" s="2">
+        <v>1</v>
+      </c>
+      <c r="D115" s="2"/>
+      <c r="E115" s="2"/>
+      <c r="F115" s="2">
+        <v>81154030000</v>
+      </c>
+      <c r="G115" s="2"/>
+      <c r="H115" s="2"/>
+    </row>
+    <row r="116" spans="1:8">
+      <c r="A116" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C116" s="2">
+        <v>1</v>
+      </c>
+      <c r="D116" s="2"/>
+      <c r="E116" s="2"/>
+      <c r="F116" s="2">
+        <v>81321186010</v>
+      </c>
+      <c r="G116" s="2"/>
+      <c r="H116" s="2"/>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="A117" s="2"/>
+      <c r="B117" s="2"/>
+      <c r="C117" s="2"/>
+      <c r="D117" s="2"/>
+      <c r="E117" s="2"/>
+      <c r="F117" s="2"/>
+      <c r="G117" s="2"/>
+      <c r="H117" s="2"/>
+    </row>
+    <row r="118" spans="1:8">
+      <c r="A118" s="2"/>
+      <c r="B118" s="2"/>
+      <c r="C118" s="2"/>
+      <c r="D118" s="2"/>
+      <c r="E118" s="2"/>
+      <c r="F118" s="2"/>
+      <c r="G118" s="2"/>
+      <c r="H118" s="2"/>
+    </row>
+    <row r="119" spans="1:8">
+      <c r="A119" s="2"/>
+      <c r="B119" s="2"/>
+      <c r="C119" s="2"/>
+      <c r="D119" s="2"/>
+      <c r="E119" s="2"/>
+      <c r="F119" s="2"/>
+      <c r="G119" s="2"/>
+      <c r="H119" s="2"/>
+    </row>
+    <row r="120" spans="1:8">
+      <c r="A120" s="2"/>
+      <c r="B120" s="2"/>
+      <c r="C120" s="2"/>
+      <c r="D120" s="2"/>
+      <c r="E120" s="2"/>
+      <c r="F120" s="2"/>
+      <c r="G120" s="2"/>
+      <c r="H120" s="2"/>
+    </row>
+    <row r="121" spans="1:8">
+      <c r="A121" s="2"/>
+      <c r="B121" s="2"/>
+      <c r="C121" s="2"/>
+      <c r="D121" s="2"/>
+      <c r="E121" s="2"/>
+      <c r="F121" s="2"/>
+      <c r="G121" s="2"/>
+      <c r="H121" s="2"/>
+    </row>
+    <row r="122" spans="1:8">
+      <c r="A122" s="2"/>
+      <c r="B122" s="2"/>
+      <c r="C122" s="2"/>
+      <c r="D122" s="2"/>
+      <c r="E122" s="2"/>
+      <c r="F122" s="2"/>
+      <c r="G122" s="2"/>
+      <c r="H122" s="2"/>
+    </row>
+    <row r="123" spans="1:8">
+      <c r="A123" s="2"/>
+      <c r="B123" s="2"/>
+      <c r="C123" s="2"/>
+      <c r="D123" s="2"/>
+      <c r="E123" s="2"/>
+      <c r="F123" s="2"/>
+      <c r="G123" s="2"/>
+      <c r="H123" s="2"/>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="A124" s="2"/>
+      <c r="B124" s="2"/>
+      <c r="C124" s="2"/>
+      <c r="D124" s="2"/>
+      <c r="E124" s="2"/>
+      <c r="F124" s="2"/>
+      <c r="G124" s="2"/>
+      <c r="H124" s="2"/>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125" s="2"/>
+      <c r="B125" s="2"/>
+      <c r="C125" s="2"/>
+      <c r="D125" s="2"/>
+      <c r="E125" s="2"/>
+      <c r="F125" s="2"/>
+      <c r="G125" s="2"/>
+      <c r="H125" s="2"/>
+    </row>
+    <row r="126" spans="1:8">
+      <c r="A126" s="2"/>
+      <c r="B126" s="2"/>
+      <c r="C126" s="2"/>
+      <c r="D126" s="2"/>
+      <c r="E126" s="2"/>
+      <c r="F126" s="2"/>
+      <c r="G126" s="2"/>
+      <c r="H126" s="2"/>
+    </row>
+    <row r="127" spans="1:8">
+      <c r="A127" s="2"/>
+      <c r="B127" s="2"/>
+      <c r="C127" s="2"/>
+      <c r="D127" s="2"/>
+      <c r="E127" s="2"/>
+      <c r="F127" s="2"/>
+      <c r="G127" s="2"/>
+      <c r="H127" s="2"/>
+    </row>
+    <row r="128" spans="1:8">
+      <c r="A128" s="2"/>
+      <c r="B128" s="2"/>
+      <c r="C128" s="2"/>
+      <c r="D128" s="2"/>
+      <c r="E128" s="2"/>
+      <c r="F128" s="2"/>
+      <c r="G128" s="2"/>
+      <c r="H128" s="2"/>
+    </row>
+    <row r="129" spans="1:8">
+      <c r="A129" s="2"/>
+      <c r="B129" s="2"/>
+      <c r="C129" s="2"/>
+      <c r="D129" s="2"/>
+      <c r="E129" s="2"/>
+      <c r="F129" s="2"/>
+      <c r="G129" s="2"/>
+      <c r="H129" s="2"/>
+    </row>
+    <row r="130" spans="1:8">
+      <c r="A130" s="2"/>
+      <c r="B130" s="2"/>
+      <c r="C130" s="2"/>
+      <c r="D130" s="2"/>
+      <c r="E130" s="2"/>
+      <c r="F130" s="2"/>
+      <c r="G130" s="2"/>
+      <c r="H130" s="2"/>
+    </row>
+    <row r="131" spans="1:8">
+      <c r="A131" s="2"/>
+      <c r="B131" s="2"/>
+      <c r="C131" s="2"/>
+      <c r="D131" s="2"/>
+      <c r="E131" s="2"/>
+      <c r="F131" s="2"/>
+      <c r="G131" s="2"/>
+      <c r="H131" s="2"/>
+    </row>
+    <row r="132" spans="1:8">
+      <c r="A132" s="2"/>
+      <c r="B132" s="2"/>
+      <c r="C132" s="2"/>
+      <c r="D132" s="2"/>
+      <c r="E132" s="2"/>
+      <c r="F132" s="2"/>
+      <c r="G132" s="2"/>
+      <c r="H132" s="2"/>
+    </row>
+    <row r="133" spans="1:8">
+      <c r="A133" s="2"/>
+      <c r="B133" s="2"/>
+      <c r="C133" s="2"/>
+      <c r="D133" s="2"/>
+      <c r="E133" s="2"/>
+      <c r="F133" s="2"/>
+      <c r="G133" s="2"/>
+      <c r="H133" s="2"/>
+    </row>
+    <row r="134" spans="1:8">
+      <c r="A134" s="2"/>
+      <c r="B134" s="2"/>
+      <c r="C134" s="2"/>
+      <c r="D134" s="2"/>
+      <c r="E134" s="2"/>
+      <c r="F134" s="2"/>
+      <c r="G134" s="2"/>
+      <c r="H134" s="2"/>
+    </row>
+    <row r="135" spans="1:8">
+      <c r="A135" s="2"/>
+      <c r="B135" s="2"/>
+      <c r="C135" s="2"/>
+      <c r="D135" s="2"/>
+      <c r="E135" s="2"/>
+      <c r="F135" s="2"/>
+      <c r="G135" s="2"/>
+      <c r="H135" s="2"/>
+    </row>
+    <row r="136" spans="1:8">
+      <c r="A136" s="2"/>
+      <c r="B136" s="2"/>
+      <c r="C136" s="2"/>
+      <c r="D136" s="2"/>
+      <c r="E136" s="2"/>
+      <c r="F136" s="2"/>
+      <c r="G136" s="2"/>
+      <c r="H136" s="2"/>
+    </row>
+    <row r="137" spans="1:8">
+      <c r="A137" s="2"/>
+      <c r="B137" s="2"/>
+      <c r="C137" s="2"/>
+      <c r="D137" s="2"/>
+      <c r="E137" s="2"/>
+      <c r="F137" s="2"/>
+      <c r="G137" s="2"/>
+      <c r="H137" s="2"/>
+    </row>
+    <row r="138" spans="1:8">
+      <c r="A138" s="2"/>
+      <c r="B138" s="2"/>
+      <c r="C138" s="2"/>
+      <c r="D138" s="2"/>
+      <c r="E138" s="2"/>
+      <c r="F138" s="2"/>
+      <c r="G138" s="2"/>
+      <c r="H138" s="2"/>
+    </row>
+    <row r="139" spans="1:8">
+      <c r="A139" s="2"/>
+      <c r="B139" s="2"/>
+      <c r="C139" s="2"/>
+      <c r="D139" s="2"/>
+      <c r="E139" s="2"/>
+      <c r="F139" s="2"/>
+      <c r="G139" s="2"/>
+      <c r="H139" s="2"/>
+    </row>
+    <row r="140" spans="1:8">
+      <c r="A140" s="2"/>
+      <c r="B140" s="2"/>
+      <c r="C140" s="2"/>
+      <c r="D140" s="2"/>
+      <c r="E140" s="2"/>
+      <c r="F140" s="2"/>
+      <c r="G140" s="2"/>
+      <c r="H140" s="2"/>
+    </row>
+    <row r="141" spans="1:8">
+      <c r="A141" s="2"/>
+      <c r="B141" s="2"/>
+      <c r="C141" s="2"/>
+      <c r="D141" s="2"/>
+      <c r="E141" s="2"/>
+      <c r="F141" s="2"/>
+      <c r="G141" s="2"/>
+      <c r="H141" s="2"/>
+    </row>
+    <row r="142" spans="1:8">
+      <c r="A142" s="2"/>
+      <c r="B142" s="2"/>
+      <c r="C142" s="2"/>
+      <c r="D142" s="2"/>
+      <c r="E142" s="2"/>
+      <c r="F142" s="2"/>
+      <c r="G142" s="2"/>
+      <c r="H142" s="2"/>
+    </row>
+    <row r="143" spans="1:8">
+      <c r="A143" s="2"/>
+      <c r="B143" s="2"/>
+      <c r="C143" s="2"/>
+      <c r="D143" s="2"/>
+      <c r="E143" s="2"/>
+      <c r="F143" s="2"/>
+      <c r="G143" s="2"/>
+      <c r="H143" s="2"/>
+    </row>
+    <row r="144" spans="1:8">
+      <c r="A144" s="2"/>
+      <c r="B144" s="2"/>
+      <c r="C144" s="2"/>
+      <c r="D144" s="2"/>
+      <c r="E144" s="2"/>
+      <c r="F144" s="2"/>
+      <c r="G144" s="2"/>
+      <c r="H144" s="2"/>
+    </row>
+    <row r="145" spans="1:8">
+      <c r="A145" s="2"/>
+      <c r="B145" s="2"/>
+      <c r="C145" s="2"/>
+      <c r="D145" s="2"/>
+      <c r="E145" s="2"/>
+      <c r="F145" s="2"/>
+      <c r="G145" s="2"/>
+      <c r="H145" s="2"/>
+    </row>
+    <row r="146" spans="1:8">
+      <c r="A146" s="2"/>
+      <c r="B146" s="2"/>
+      <c r="C146" s="2"/>
+      <c r="D146" s="2"/>
+      <c r="E146" s="2"/>
+      <c r="F146" s="2"/>
+      <c r="G146" s="2"/>
+      <c r="H146" s="2"/>
+    </row>
+    <row r="147" spans="1:8">
+      <c r="A147" s="2"/>
+      <c r="B147" s="2"/>
+      <c r="C147" s="2"/>
+      <c r="D147" s="2"/>
+      <c r="E147" s="2"/>
+      <c r="F147" s="2"/>
+      <c r="G147" s="2"/>
+      <c r="H147" s="2"/>
+    </row>
+    <row r="148" spans="1:8">
+      <c r="A148" s="2"/>
+      <c r="B148" s="2"/>
+      <c r="C148" s="2"/>
+      <c r="D148" s="2"/>
+      <c r="E148" s="2"/>
+      <c r="F148" s="2"/>
+      <c r="G148" s="2"/>
+      <c r="H148" s="2"/>
+    </row>
+    <row r="149" spans="1:8">
+      <c r="A149" s="2"/>
+      <c r="B149" s="2"/>
+      <c r="C149" s="2"/>
+      <c r="D149" s="2"/>
+      <c r="E149" s="2"/>
+      <c r="F149" s="2"/>
+      <c r="G149" s="2"/>
+      <c r="H149" s="2"/>
+    </row>
+    <row r="150" spans="1:8">
+      <c r="A150" s="2"/>
+      <c r="B150" s="2"/>
+      <c r="C150" s="2"/>
+      <c r="D150" s="2"/>
+      <c r="E150" s="2"/>
+      <c r="F150" s="2"/>
+      <c r="G150" s="2"/>
+      <c r="H150" s="2"/>
+    </row>
+    <row r="151" spans="1:8">
+      <c r="A151" s="2"/>
+      <c r="B151" s="2"/>
+      <c r="C151" s="2"/>
+      <c r="D151" s="2"/>
+      <c r="E151" s="2"/>
+      <c r="F151" s="2"/>
+      <c r="G151" s="2"/>
+      <c r="H151" s="2"/>
+    </row>
+    <row r="152" spans="1:8">
+      <c r="A152" s="2"/>
+      <c r="B152" s="2"/>
+      <c r="C152" s="2"/>
+      <c r="D152" s="2"/>
+      <c r="E152" s="2"/>
+      <c r="F152" s="2"/>
+      <c r="G152" s="2"/>
+      <c r="H152" s="2"/>
+    </row>
+    <row r="153" spans="1:8">
+      <c r="A153" s="2"/>
+      <c r="B153" s="2"/>
+      <c r="C153" s="2"/>
+      <c r="D153" s="2"/>
+      <c r="E153" s="2"/>
+      <c r="F153" s="2"/>
+      <c r="G153" s="2"/>
+      <c r="H153" s="2"/>
+    </row>
+    <row r="154" spans="1:8">
+      <c r="A154" s="2"/>
+      <c r="B154" s="2"/>
+      <c r="C154" s="2"/>
+      <c r="D154" s="2"/>
+      <c r="E154" s="2"/>
+      <c r="F154" s="2"/>
+      <c r="G154" s="2"/>
+      <c r="H154" s="2"/>
+    </row>
+    <row r="155" spans="1:8">
+      <c r="A155" s="2"/>
+      <c r="B155" s="2"/>
+      <c r="C155" s="2"/>
+      <c r="D155" s="2"/>
+      <c r="E155" s="2"/>
+      <c r="F155" s="2"/>
+      <c r="G155" s="2"/>
+      <c r="H155" s="2"/>
+    </row>
+    <row r="156" spans="1:8">
+      <c r="A156" s="2"/>
+      <c r="B156" s="2"/>
+      <c r="C156" s="2"/>
+      <c r="D156" s="2"/>
+      <c r="E156" s="2"/>
+      <c r="F156" s="2"/>
+      <c r="G156" s="2"/>
+      <c r="H156" s="2"/>
+    </row>
+    <row r="157" spans="1:8">
+      <c r="A157" s="2"/>
+      <c r="B157" s="2"/>
+      <c r="C157" s="2"/>
+      <c r="D157" s="2"/>
+      <c r="E157" s="2"/>
+      <c r="F157" s="2"/>
+      <c r="G157" s="2"/>
+      <c r="H157" s="2"/>
+    </row>
+    <row r="158" spans="1:8">
+      <c r="A158" s="2"/>
+      <c r="B158" s="2"/>
+      <c r="C158" s="2"/>
+      <c r="D158" s="2"/>
+      <c r="E158" s="2"/>
+      <c r="F158" s="2"/>
+      <c r="G158" s="2"/>
+      <c r="H158" s="2"/>
+    </row>
+    <row r="159" spans="1:8">
+      <c r="A159" s="2"/>
+      <c r="B159" s="2"/>
+      <c r="C159" s="2"/>
+      <c r="D159" s="2"/>
+      <c r="E159" s="2"/>
+      <c r="F159" s="2"/>
+      <c r="G159" s="2"/>
+      <c r="H159" s="2"/>
+    </row>
+    <row r="160" spans="1:8">
+      <c r="A160" s="2"/>
+      <c r="B160" s="2"/>
+      <c r="C160" s="2"/>
+      <c r="D160" s="2"/>
+      <c r="E160" s="2"/>
+      <c r="F160" s="2"/>
+      <c r="G160" s="2"/>
+      <c r="H160" s="2"/>
+    </row>
+    <row r="161" spans="1:8">
+      <c r="A161" s="2"/>
+      <c r="B161" s="2"/>
+      <c r="C161" s="2"/>
+      <c r="D161" s="2"/>
+      <c r="E161" s="2"/>
+      <c r="F161" s="2"/>
+      <c r="G161" s="2"/>
+      <c r="H161" s="2"/>
+    </row>
+    <row r="162" spans="1:8">
+      <c r="A162" s="2"/>
+      <c r="B162" s="2"/>
+      <c r="C162" s="2"/>
+      <c r="D162" s="2"/>
+      <c r="E162" s="2"/>
+      <c r="F162" s="2"/>
+      <c r="G162" s="2"/>
+      <c r="H162" s="2"/>
+    </row>
+    <row r="163" spans="1:8">
+      <c r="A163" s="2"/>
+      <c r="B163" s="2"/>
+      <c r="C163" s="2"/>
+      <c r="D163" s="2"/>
+      <c r="E163" s="2"/>
+      <c r="F163" s="2"/>
+      <c r="G163" s="2"/>
+      <c r="H163" s="2"/>
+    </row>
+    <row r="164" spans="1:8">
+      <c r="A164" s="2"/>
+      <c r="B164" s="2"/>
+      <c r="C164" s="2"/>
+      <c r="D164" s="2"/>
+      <c r="E164" s="2"/>
+      <c r="F164" s="2"/>
+      <c r="G164" s="2"/>
+      <c r="H164" s="2"/>
+    </row>
+    <row r="165" spans="1:8">
+      <c r="A165" s="2"/>
+      <c r="B165" s="2"/>
+      <c r="C165" s="2"/>
+      <c r="D165" s="2"/>
+      <c r="E165" s="2"/>
+      <c r="F165" s="2"/>
+      <c r="G165" s="2"/>
+      <c r="H165" s="2"/>
+    </row>
+    <row r="166" spans="1:8">
+      <c r="A166" s="2"/>
+      <c r="B166" s="2"/>
+      <c r="C166" s="2"/>
+      <c r="D166" s="2"/>
+      <c r="E166" s="2"/>
+      <c r="F166" s="2"/>
+      <c r="G166" s="2"/>
+      <c r="H166" s="2"/>
+    </row>
+    <row r="167" spans="1:8">
+      <c r="A167" s="2"/>
+      <c r="B167" s="2"/>
+      <c r="C167" s="2"/>
+      <c r="D167" s="2"/>
+      <c r="E167" s="2"/>
+      <c r="F167" s="2"/>
+      <c r="G167" s="2"/>
+      <c r="H167" s="2"/>
+    </row>
+    <row r="168" spans="1:8">
+      <c r="A168" s="2"/>
+      <c r="B168" s="2"/>
+      <c r="C168" s="2"/>
+      <c r="D168" s="2"/>
+      <c r="E168" s="2"/>
+      <c r="F168" s="2"/>
+      <c r="G168" s="2"/>
+      <c r="H168" s="2"/>
+    </row>
+    <row r="169" spans="1:8">
+      <c r="A169" s="2"/>
+      <c r="B169" s="2"/>
+      <c r="C169" s="2"/>
+      <c r="D169" s="2"/>
+      <c r="E169" s="2"/>
+      <c r="F169" s="2"/>
+      <c r="G169" s="2"/>
+      <c r="H169" s="2"/>
+    </row>
+    <row r="170" spans="1:8">
+      <c r="A170" s="2"/>
+      <c r="B170" s="2"/>
+      <c r="C170" s="2"/>
+      <c r="D170" s="2"/>
+      <c r="E170" s="2"/>
+      <c r="F170" s="2"/>
+      <c r="G170" s="2"/>
+      <c r="H170" s="2"/>
+    </row>
+    <row r="171" spans="1:8">
+      <c r="A171" s="2"/>
+      <c r="B171" s="2"/>
+      <c r="C171" s="2"/>
+      <c r="D171" s="2"/>
+      <c r="E171" s="2"/>
+      <c r="F171" s="2"/>
+      <c r="G171" s="2"/>
+      <c r="H171" s="2"/>
+    </row>
+    <row r="172" spans="1:8">
+      <c r="A172" s="2"/>
+      <c r="B172" s="2"/>
+      <c r="C172" s="2"/>
+      <c r="D172" s="2"/>
+      <c r="E172" s="2"/>
+      <c r="F172" s="2"/>
+      <c r="G172" s="2"/>
+      <c r="H172" s="2"/>
+    </row>
+    <row r="173" spans="1:8">
+      <c r="A173" s="2"/>
+      <c r="B173" s="2"/>
+      <c r="C173" s="2"/>
+      <c r="D173" s="2"/>
+      <c r="E173" s="2"/>
+      <c r="F173" s="2"/>
+      <c r="G173" s="2"/>
+      <c r="H173" s="2"/>
+    </row>
+    <row r="174" spans="1:8">
+      <c r="A174" s="2"/>
+      <c r="B174" s="2"/>
+      <c r="C174" s="2"/>
+      <c r="D174" s="2"/>
+      <c r="E174" s="2"/>
+      <c r="F174" s="2"/>
+      <c r="G174" s="2"/>
+      <c r="H174" s="2"/>
+    </row>
+    <row r="175" spans="1:8">
+      <c r="A175" s="2"/>
+      <c r="B175" s="2"/>
+      <c r="C175" s="2"/>
+      <c r="D175" s="2"/>
+      <c r="E175" s="2"/>
+      <c r="F175" s="2"/>
+      <c r="G175" s="2"/>
+      <c r="H175" s="2"/>
+    </row>
+    <row r="176" spans="1:8">
+      <c r="A176" s="2"/>
+      <c r="B176" s="2"/>
+      <c r="C176" s="2"/>
+      <c r="D176" s="2"/>
+      <c r="E176" s="2"/>
+      <c r="F176" s="2"/>
+      <c r="G176" s="2"/>
+      <c r="H176" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
